--- a/Module2_chart.xlsx
+++ b/Module2_chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\silva\iCloudDrive\UHCL\MGMT 52A2 - Data Visualization for Managers\Concept Checks and Applied Analyses\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E395D49-ED59-49D4-BDB5-0C23AEE96B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E496E59-22B1-4E33-A2C1-D562FFB19147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{9A08DE92-CE0E-485F-93AB-4CD7A7EC4088}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2189,7 +2189,7 @@
         <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
         <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
             <a:lnSpc>
               <a:spcPct val="100000"/>
             </a:lnSpc>
@@ -2207,14 +2207,15 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Operations Requires Attention: Lowest Department Performance Score</a:t>
+            <a:rPr lang="en-US" sz="1050"/>
+            <a:t>Operations Has the Lowest Average Performance Score</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="1050">
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
       </cdr:txBody>
     </cdr:sp>
@@ -2709,7 +2710,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4A3D68C-07BD-4466-9A53-455715C9107E}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4A3D68C-07BD-4466-9A53-455715C9107E}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
